--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488114_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488114_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1607</v>
+        <v>11.9559</v>
       </c>
       <c r="E2" t="n">
-        <v>9.570600000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5901</v>
+        <v>3.5059</v>
       </c>
       <c r="G2" t="n">
         <v>3.7138</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6273</v>
+        <v>1.4225</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4597</v>
+        <v>1.3391</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1676</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
         <v>5.432</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6912</v>
+        <v>8.8035</v>
       </c>
       <c r="E3" t="n">
         <v>5.534</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1571</v>
+        <v>3.2695</v>
       </c>
       <c r="G3" t="n">
         <v>4.469</v>
@@ -688,13 +688,13 @@
         <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1101</v>
+        <v>1.2224</v>
       </c>
       <c r="T3" t="n">
         <v>1.1638</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0537</v>
+        <v>0.0586</v>
       </c>
       <c r="V3" t="n">
         <v>0.337</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2111</v>
+        <v>6.9242</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4142</v>
+        <v>3.1273</v>
       </c>
       <c r="F4" t="n">
         <v>3.7969</v>
@@ -766,10 +766,10 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1452</v>
+        <v>1.8583</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3047</v>
+        <v>1.0178</v>
       </c>
       <c r="U4" t="n">
         <v>0.8405</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9989</v>
+        <v>5.824</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3626</v>
+        <v>3.1763</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6364</v>
+        <v>2.6478</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5077</v>
+        <v>3.2737</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0084</v>
+        <v>2.1334</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4992</v>
+        <v>1.1403</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6528</v>
+        <v>2.9806</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2516</v>
+        <v>2.2535</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5988</v>
+        <v>0.7271</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8549</v>
+        <v>0.2931</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7569</v>
+        <v>-0.1201</v>
       </c>
       <c r="O5" t="n">
-        <v>1.098</v>
+        <v>0.4132</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5548</v>
+        <v>1.1628</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0925</v>
+        <v>1.1868</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4623</v>
+        <v>-0.024</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3329</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5994</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7574</v>
+        <v>5.2142</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2781</v>
+        <v>1.4995</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4793</v>
+        <v>3.7147</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2737</v>
+        <v>1.7869</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1334</v>
+        <v>0.0497</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1403</v>
+        <v>1.7372</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9806</v>
+        <v>1.162</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2535</v>
+        <v>0.5114</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7271</v>
+        <v>0.6506</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2931</v>
+        <v>0.625</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1201</v>
+        <v>-0.4617</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>1.0866</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R6" t="n">
         <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0962</v>
+        <v>1.9208</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2886</v>
+        <v>1.2097</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1924</v>
+        <v>0.7111</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6145</v>
+        <v>4.9032</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7032</v>
+        <v>1.5476</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9113</v>
+        <v>3.3556</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7869</v>
+        <v>2.5077</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0497</v>
+        <v>2.0084</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7372</v>
+        <v>0.4992</v>
       </c>
       <c r="J7" t="n">
-        <v>1.162</v>
+        <v>0.6528</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5114</v>
+        <v>1.2516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6506</v>
+        <v>-0.5988</v>
       </c>
       <c r="M7" t="n">
-        <v>0.625</v>
+        <v>1.8549</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4617</v>
+        <v>0.7569</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0866</v>
+        <v>1.098</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1805</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3211</v>
+        <v>1.4591</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4134</v>
+        <v>1.2776</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9077</v>
+        <v>0.1815</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.674</v>
+        <v>1.3329</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.674</v>
+        <v>1.5994</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3816</v>
+        <v>3.761</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2693</v>
+        <v>-0.8619</v>
       </c>
       <c r="F8" t="n">
-        <v>4.651</v>
+        <v>4.6229</v>
       </c>
       <c r="G8" t="n">
         <v>0.7207</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0662</v>
+        <v>2.4456</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1087</v>
+        <v>1.5161</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9576</v>
+        <v>0.9295</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9907</v>
+        <v>2.155</v>
       </c>
       <c r="E9" t="n">
-        <v>0.507</v>
+        <v>0.6713</v>
       </c>
       <c r="F9" t="n">
         <v>1.4837</v>
@@ -1156,10 +1156,10 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.334</v>
+        <v>-0.1698</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1286</v>
+        <v>0.2929</v>
       </c>
       <c r="U9" t="n">
         <v>-0.4626</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.132</v>
+        <v>1.946</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0481</v>
+        <v>-1.3745</v>
       </c>
       <c r="F10" t="n">
-        <v>3.18</v>
+        <v>3.3204</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8874</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4276</v>
+        <v>0.3864</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>0.5526</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3066</v>
+        <v>-0.1662</v>
       </c>
       <c r="V10" t="n">
         <v>0.2666</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS  LAJARA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.9337</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.2744</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.2081</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4875</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.0212</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.5337</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.1432</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.2112</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.3544</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.6307</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.8207</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.7654</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.972</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.2066</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>S. TORRECILLAS  LAJARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4044</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4387</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8431</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4875</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0212</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1432</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2112</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3544</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6307</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8207</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2361</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8077</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5716</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9094</v>
+        <v>-1.717</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6479</v>
+        <v>-0.4837</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2614</v>
+        <v>-1.2334</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9926</v>
@@ -1468,13 +1468,13 @@
         <v>0.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1061</v>
+        <v>0.0863</v>
       </c>
       <c r="T13" t="n">
-        <v>0.011</v>
+        <v>0.1753</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9883</v>
+        <v>-1.9468</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1128</v>
+        <v>-1.8467</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1246</v>
+        <v>-0.1001</v>
       </c>
       <c r="G14" t="n">
         <v>-2.4023</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0264</v>
+        <v>0.0679</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1762</v>
+        <v>0.09</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2026</v>
+        <v>-0.0221</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6036</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>49.0501</v>
+        <v>49.36219999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>18.4582</v>
+        <v>18.7701</v>
       </c>
       <c r="F15" t="n">
-        <v>30.59209999999999</v>
+        <v>30.592</v>
       </c>
       <c r="G15" t="n">
         <v>18.0762</v>
@@ -1594,7 +1594,7 @@
         <v>14.8232</v>
       </c>
       <c r="I15" t="n">
-        <v>3.253100000000001</v>
+        <v>3.2531</v>
       </c>
       <c r="J15" t="n">
         <v>8.703699999999998</v>
@@ -1624,16 +1624,16 @@
         <v>22.7957</v>
       </c>
       <c r="S15" t="n">
-        <v>12.3157</v>
+        <v>12.6277</v>
       </c>
       <c r="T15" t="n">
-        <v>10.4815</v>
+        <v>10.7937</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8343</v>
+        <v>1.834</v>
       </c>
       <c r="V15" t="n">
-        <v>6.764799999999999</v>
+        <v>6.764800000000001</v>
       </c>
       <c r="W15" t="n">
         <v>10.1749</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0335</v>
+        <v>2.6193</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4193</v>
+        <v>2.2343</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6142</v>
+        <v>0.385</v>
       </c>
       <c r="G16" t="n">
         <v>1.1266</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6788</v>
+        <v>-1.0931</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0608</v>
+        <v>-0.2458</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6181</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6558</v>
+        <v>-2.2061</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1289</v>
+        <v>-1.7589</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5269</v>
+        <v>-0.4472</v>
       </c>
       <c r="G17" t="n">
         <v>-3.1146</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2695</v>
+        <v>-0.2808</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2101</v>
+        <v>0.5802</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9406</v>
+        <v>-0.861</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6029</v>
+        <v>-2.3887</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7325</v>
+        <v>-0.6307</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8703</v>
+        <v>-1.758</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2893</v>
@@ -1858,13 +1858,13 @@
         <v>0.3964</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1769</v>
+        <v>-0.9627</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7401</v>
+        <v>-0.6278</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5331</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. AGUILAR GARCIA</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6246</v>
+        <v>-2.79</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6687</v>
+        <v>-3.9795</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9559</v>
+        <v>1.1894</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.449</v>
+        <v>0.4331</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6511</v>
+        <v>-0.0433</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.4764</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0536</v>
+        <v>0.4409</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.3455</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6791</v>
+        <v>-0.9046</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3953</v>
+        <v>-0.0078</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2766</v>
+        <v>-1.3889</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1187</v>
+        <v>1.3811</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7929</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3828</v>
+        <v>-1.6483</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.624</v>
+        <v>-0.4559</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7588</v>
+        <v>-1.1924</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>A. AGUILAR GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7023</v>
+        <v>-3.1329</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8963</v>
+        <v>-1.2612</v>
       </c>
       <c r="F20" t="n">
-        <v>1.194</v>
+        <v>-1.8717</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4331</v>
+        <v>-1.449</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0433</v>
+        <v>-0.6511</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4764</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4409</v>
+        <v>-0.0536</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3455</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9046</v>
+        <v>-0.6791</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0078</v>
+        <v>-1.3953</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3889</v>
+        <v>-1.2766</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3811</v>
+        <v>-0.1187</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9822</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.5605</v>
+        <v>-0.8911</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3727</v>
+        <v>-0.2165</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1878</v>
+        <v>-0.6746</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8639</v>
+        <v>-5.4427</v>
       </c>
       <c r="E21" t="n">
         <v>-4.0053</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8585</v>
+        <v>-1.4373</v>
       </c>
       <c r="G21" t="n">
         <v>-0.549</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4099</v>
+        <v>-1.9887</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3816</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.0283</v>
+        <v>-1.6071</v>
       </c>
       <c r="V21" t="n">
         <v>0.2666</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7436</v>
+        <v>-6.8455</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9039</v>
+        <v>-4.0058</v>
       </c>
       <c r="F22" t="n">
         <v>-2.8397</v>
@@ -2170,10 +2170,10 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1673</v>
+        <v>-1.2691</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2568</v>
+        <v>-0.3587</v>
       </c>
       <c r="U22" t="n">
         <v>-0.9104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6892</v>
+        <v>-7.8623</v>
       </c>
       <c r="E23" t="n">
         <v>-6.2696</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4197</v>
+        <v>-1.5927</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6964</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9402</v>
+        <v>-1.1132</v>
       </c>
       <c r="T23" t="n">
         <v>0.0479</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9881</v>
+        <v>-1.1612</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4846</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.611800000000001</v>
+        <v>-8.715</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6085</v>
+        <v>-4.016</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0033</v>
+        <v>-4.699</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7287</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6254</v>
+        <v>-0.7286</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4223</v>
+        <v>0.0148</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0477</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-2.6808</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.5896</v>
+        <v>-11.6072</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.7975</v>
+        <v>-6.8994</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7921</v>
+        <v>-4.7078</v>
       </c>
       <c r="G25" t="n">
         <v>-5.292</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6434</v>
+        <v>-1.661</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3816</v>
+        <v>-0.4835</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2618</v>
+        <v>-1.1775</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0772</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-49.0502</v>
+        <v>-48.3711</v>
       </c>
       <c r="E26" t="n">
-        <v>-30.5919</v>
+        <v>-30.5921</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.4582</v>
+        <v>-17.779</v>
       </c>
       <c r="G26" t="n">
         <v>-18.0762</v>
@@ -2458,7 +2458,7 @@
         <v>-9.3725</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4868000000000006</v>
+        <v>-0.4868000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>-8.8856</v>
@@ -2482,13 +2482,13 @@
         <v>10.9022</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.3157</v>
+        <v>-11.6366</v>
       </c>
       <c r="T26" t="n">
         <v>-1.834</v>
       </c>
       <c r="U26" t="n">
-        <v>-10.4817</v>
+        <v>-9.8027</v>
       </c>
       <c r="V26" t="n">
         <v>-6.764699999999999</v>
